--- a/NBFC-MF/Borrowers/Renita_Daily.xlsx
+++ b/NBFC-MF/Borrowers/Renita_Daily.xlsx
@@ -1113,171 +1113,181 @@
       <c r="L11" s="22"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="2"/>
-      <c r="B12" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A12" s="2">
+        <v>46202</v>
+      </c>
+      <c r="B12" s="23">
+        <f t="shared" si="3"/>
+        <v>11</v>
       </c>
       <c r="C12" s="3"/>
-      <c r="D12" s="4" t="str">
+      <c r="D12" s="4">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E12" s="4" t="str">
+        <v>180</v>
+      </c>
+      <c r="E12" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F12" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G12" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H12" s="4" t="str">
+        <v>52.140867683141181</v>
+      </c>
+      <c r="F12" s="4">
+        <f t="shared" si="5"/>
+        <v>127.85913231685882</v>
+      </c>
+      <c r="G12" s="4">
+        <f t="shared" si="4"/>
+        <v>16615.179195964247</v>
+      </c>
+      <c r="H12" s="4">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1384.8208040357531</v>
       </c>
       <c r="J12" s="9" t="s">
         <v>16</v>
       </c>
       <c r="K12" s="10">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>10</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="19"/>
-      <c r="B13" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A13" s="19">
+        <v>46202</v>
+      </c>
+      <c r="B13" s="24">
+        <f t="shared" si="3"/>
+        <v>12</v>
       </c>
       <c r="C13" s="20"/>
-      <c r="D13" s="21" t="str">
+      <c r="D13" s="21">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E13" s="21" t="str">
+        <v>180</v>
+      </c>
+      <c r="E13" s="21">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F13" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G13" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H13" s="21" t="str">
+        <v>51.74269108164863</v>
+      </c>
+      <c r="F13" s="21">
+        <f t="shared" si="5"/>
+        <v>128.25730891835138</v>
+      </c>
+      <c r="G13" s="21">
+        <f t="shared" si="4"/>
+        <v>16486.921887045897</v>
+      </c>
+      <c r="H13" s="21">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1513.0781129541028</v>
       </c>
       <c r="J13" s="25" t="s">
         <v>22</v>
       </c>
       <c r="K13" s="12">
         <f>(K10*K9)-K9*K12</f>
-        <v>19800</v>
+        <v>15660</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="2"/>
-      <c r="B14" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A14" s="2">
+        <v>46202</v>
+      </c>
+      <c r="B14" s="23">
+        <f t="shared" si="3"/>
+        <v>13</v>
       </c>
       <c r="C14" s="3"/>
-      <c r="D14" s="4" t="str">
+      <c r="D14" s="4">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E14" s="4" t="str">
+        <v>180</v>
+      </c>
+      <c r="E14" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F14" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G14" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H14" s="4" t="str">
+        <v>51.34327448577239</v>
+      </c>
+      <c r="F14" s="4">
+        <f t="shared" si="5"/>
+        <v>128.65672551422762</v>
+      </c>
+      <c r="G14" s="4">
+        <f t="shared" si="4"/>
+        <v>16358.26516153167</v>
+      </c>
+      <c r="H14" s="4">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1641.7348384683301</v>
       </c>
       <c r="J14" s="11" t="s">
         <v>23</v>
       </c>
       <c r="K14" s="12">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>16743.038328281105</v>
+        <v>13699.308972116984</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="19"/>
-      <c r="B15" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A15" s="19">
+        <v>46202</v>
+      </c>
+      <c r="B15" s="24">
+        <f t="shared" si="3"/>
+        <v>14</v>
       </c>
       <c r="C15" s="20"/>
-      <c r="D15" s="21" t="str">
+      <c r="D15" s="21">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E15" s="21" t="str">
+        <v>180</v>
+      </c>
+      <c r="E15" s="21">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F15" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G15" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H15" s="21" t="str">
+        <v>50.942614033944338</v>
+      </c>
+      <c r="F15" s="21">
+        <f t="shared" si="5"/>
+        <v>129.05738596605568</v>
+      </c>
+      <c r="G15" s="21">
+        <f t="shared" si="4"/>
+        <v>16229.207775565614</v>
+      </c>
+      <c r="H15" s="21">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1770.7922244343863</v>
       </c>
       <c r="J15" s="13" t="s">
         <v>6</v>
       </c>
       <c r="K15" s="14">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>1256.9616717188946</v>
+        <v>4300.6910278830164</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="2"/>
-      <c r="B16" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A16" s="2">
+        <v>46202</v>
+      </c>
+      <c r="B16" s="23">
+        <f t="shared" si="3"/>
+        <v>15</v>
       </c>
       <c r="C16" s="3"/>
-      <c r="D16" s="4" t="str">
+      <c r="D16" s="4">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E16" s="4" t="str">
+        <v>180</v>
+      </c>
+      <c r="E16" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F16" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G16" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H16" s="4" t="str">
+        <v>50.540705852570717</v>
+      </c>
+      <c r="F16" s="4">
+        <f t="shared" si="5"/>
+        <v>129.45929414742929</v>
+      </c>
+      <c r="G16" s="4">
+        <f t="shared" si="4"/>
+        <v>16099.748481418184</v>
+      </c>
+      <c r="H16" s="4">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1900.2515185818156</v>
       </c>
       <c r="J16" s="15" t="s">
         <v>18</v>
@@ -1288,31 +1298,33 @@
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" s="19"/>
-      <c r="B17" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A17" s="19">
+        <v>46202</v>
+      </c>
+      <c r="B17" s="24">
+        <f t="shared" si="3"/>
+        <v>16</v>
       </c>
       <c r="C17" s="20"/>
-      <c r="D17" s="21" t="str">
+      <c r="D17" s="21">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E17" s="21" t="str">
+        <v>180</v>
+      </c>
+      <c r="E17" s="21">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F17" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G17" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H17" s="21" t="str">
+        <v>50.137546055994719</v>
+      </c>
+      <c r="F17" s="21">
+        <f t="shared" si="5"/>
+        <v>129.86245394400527</v>
+      </c>
+      <c r="G17" s="21">
+        <f t="shared" si="4"/>
+        <v>15969.886027474178</v>
+      </c>
+      <c r="H17" s="21">
         <f t="shared" si="2"/>
-        <v/>
+        <v>2030.1139725258217</v>
       </c>
       <c r="J17" s="17" t="s">
         <v>19</v>
@@ -1323,481 +1335,515 @@
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" s="2"/>
-      <c r="B18" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A18" s="2">
+        <v>46202</v>
+      </c>
+      <c r="B18" s="23">
+        <f t="shared" si="3"/>
+        <v>17</v>
       </c>
       <c r="C18" s="3"/>
-      <c r="D18" s="4" t="str">
+      <c r="D18" s="4">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E18" s="4" t="str">
+        <v>180</v>
+      </c>
+      <c r="E18" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F18" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G18" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H18" s="4" t="str">
+        <v>49.733130746458869</v>
+      </c>
+      <c r="F18" s="4">
+        <f t="shared" si="5"/>
+        <v>130.26686925354113</v>
+      </c>
+      <c r="G18" s="4">
+        <f t="shared" si="4"/>
+        <v>15839.619158220637</v>
+      </c>
+      <c r="H18" s="4">
         <f t="shared" si="2"/>
-        <v/>
+        <v>2160.3808417793625</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="19"/>
-      <c r="B19" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A19" s="19">
+        <v>46202</v>
+      </c>
+      <c r="B19" s="24">
+        <f t="shared" si="3"/>
+        <v>18</v>
       </c>
       <c r="C19" s="20"/>
-      <c r="D19" s="21" t="str">
+      <c r="D19" s="21">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E19" s="21" t="str">
+        <v>180</v>
+      </c>
+      <c r="E19" s="21">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F19" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G19" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H19" s="21" t="str">
+        <v>49.327456014067373</v>
+      </c>
+      <c r="F19" s="21">
+        <f t="shared" si="5"/>
+        <v>130.67254398593263</v>
+      </c>
+      <c r="G19" s="21">
+        <f t="shared" si="4"/>
+        <v>15708.946614234705</v>
+      </c>
+      <c r="H19" s="21">
         <f t="shared" si="2"/>
-        <v/>
+        <v>2291.0533857652954</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A20" s="2"/>
-      <c r="B20" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A20" s="2">
+        <v>46202</v>
+      </c>
+      <c r="B20" s="23">
+        <f t="shared" si="3"/>
+        <v>19</v>
       </c>
       <c r="C20" s="3"/>
-      <c r="D20" s="4" t="str">
+      <c r="D20" s="4">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E20" s="4" t="str">
+        <v>180</v>
+      </c>
+      <c r="E20" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F20" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G20" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H20" s="4" t="str">
+        <v>48.920517936748318</v>
+      </c>
+      <c r="F20" s="4">
+        <f t="shared" si="5"/>
+        <v>131.07948206325167</v>
+      </c>
+      <c r="G20" s="4">
+        <f t="shared" si="4"/>
+        <v>15577.867132171454</v>
+      </c>
+      <c r="H20" s="4">
         <f t="shared" si="2"/>
-        <v/>
+        <v>2422.1328678285463</v>
       </c>
       <c r="J20" s="22"/>
       <c r="K20" s="22"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A21" s="19"/>
-      <c r="B21" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A21" s="19">
+        <v>46202</v>
+      </c>
+      <c r="B21" s="24">
+        <f t="shared" si="3"/>
+        <v>20</v>
       </c>
       <c r="C21" s="20"/>
-      <c r="D21" s="21" t="str">
+      <c r="D21" s="21">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E21" s="21" t="str">
+        <v>180</v>
+      </c>
+      <c r="E21" s="21">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F21" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G21" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H21" s="21" t="str">
+        <v>48.512312580215742</v>
+      </c>
+      <c r="F21" s="21">
+        <f t="shared" si="5"/>
+        <v>131.48768741978427</v>
+      </c>
+      <c r="G21" s="21">
+        <f t="shared" si="4"/>
+        <v>15446.37944475167</v>
+      </c>
+      <c r="H21" s="21">
         <f t="shared" si="2"/>
-        <v/>
+        <v>2553.6205552483298</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A22" s="2"/>
-      <c r="B22" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A22" s="2">
+        <v>46202</v>
+      </c>
+      <c r="B22" s="23">
+        <f t="shared" si="3"/>
+        <v>21</v>
       </c>
       <c r="C22" s="3"/>
-      <c r="D22" s="4" t="str">
+      <c r="D22" s="4">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E22" s="4" t="str">
+        <v>180</v>
+      </c>
+      <c r="E22" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F22" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G22" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H22" s="4" t="str">
+        <v>48.102835997931585</v>
+      </c>
+      <c r="F22" s="4">
+        <f t="shared" si="5"/>
+        <v>131.89716400206842</v>
+      </c>
+      <c r="G22" s="4">
+        <f t="shared" si="4"/>
+        <v>15314.482280749602</v>
+      </c>
+      <c r="H22" s="4">
         <f t="shared" si="2"/>
-        <v/>
+        <v>2685.5177192503979</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" s="19"/>
-      <c r="B23" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A23" s="19">
+        <v>46202</v>
+      </c>
+      <c r="B23" s="24">
+        <f t="shared" si="3"/>
+        <v>22</v>
       </c>
       <c r="C23" s="20"/>
-      <c r="D23" s="21" t="str">
+      <c r="D23" s="21">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E23" s="21" t="str">
+        <v>180</v>
+      </c>
+      <c r="E23" s="21">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F23" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G23" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H23" s="21" t="str">
+        <v>47.692084231067568</v>
+      </c>
+      <c r="F23" s="21">
+        <f t="shared" si="5"/>
+        <v>132.30791576893245</v>
+      </c>
+      <c r="G23" s="21">
+        <f t="shared" si="4"/>
+        <v>15182.17436498067</v>
+      </c>
+      <c r="H23" s="21">
         <f t="shared" si="2"/>
-        <v/>
+        <v>2817.8256350193296</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24" s="2"/>
-      <c r="B24" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A24" s="2">
+        <v>46202</v>
+      </c>
+      <c r="B24" s="23">
+        <f t="shared" si="3"/>
+        <v>23</v>
       </c>
       <c r="C24" s="3"/>
-      <c r="D24" s="4" t="str">
+      <c r="D24" s="4">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E24" s="4" t="str">
+        <v>180</v>
+      </c>
+      <c r="E24" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F24" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G24" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H24" s="4" t="str">
+        <v>47.280053308466897</v>
+      </c>
+      <c r="F24" s="4">
+        <f t="shared" si="5"/>
+        <v>132.7199466915331</v>
+      </c>
+      <c r="G24" s="4">
+        <f t="shared" si="4"/>
+        <v>15049.454418289137</v>
+      </c>
+      <c r="H24" s="4">
         <f t="shared" si="2"/>
-        <v/>
+        <v>2950.5455817108632</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A25" s="19"/>
-      <c r="B25" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A25" s="19">
+        <v>46202</v>
+      </c>
+      <c r="B25" s="24">
+        <f t="shared" si="3"/>
+        <v>24</v>
       </c>
       <c r="C25" s="20"/>
-      <c r="D25" s="21" t="str">
+      <c r="D25" s="21">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E25" s="21" t="str">
+        <v>180</v>
+      </c>
+      <c r="E25" s="21">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F25" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G25" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H25" s="21" t="str">
+        <v>46.866739246605867</v>
+      </c>
+      <c r="F25" s="21">
+        <f t="shared" si="5"/>
+        <v>133.13326075339413</v>
+      </c>
+      <c r="G25" s="21">
+        <f t="shared" si="4"/>
+        <v>14916.321157535742</v>
+      </c>
+      <c r="H25" s="21">
         <f t="shared" si="2"/>
-        <v/>
+        <v>3083.6788424642582</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A26" s="2"/>
-      <c r="B26" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A26" s="2">
+        <v>46202</v>
+      </c>
+      <c r="B26" s="23">
+        <f t="shared" si="3"/>
+        <v>25</v>
       </c>
       <c r="C26" s="3"/>
-      <c r="D26" s="4" t="str">
+      <c r="D26" s="4">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E26" s="4" t="str">
+        <v>180</v>
+      </c>
+      <c r="E26" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F26" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G26" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H26" s="4" t="str">
+        <v>46.452138049555359</v>
+      </c>
+      <c r="F26" s="4">
+        <f t="shared" si="5"/>
+        <v>133.54786195044466</v>
+      </c>
+      <c r="G26" s="4">
+        <f t="shared" si="4"/>
+        <v>14782.773295585297</v>
+      </c>
+      <c r="H26" s="4">
         <f t="shared" si="2"/>
-        <v/>
+        <v>3217.2267044147029</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A27" s="19"/>
-      <c r="B27" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A27" s="19">
+        <v>46202</v>
+      </c>
+      <c r="B27" s="24">
+        <f t="shared" si="3"/>
+        <v>26</v>
       </c>
       <c r="C27" s="20"/>
-      <c r="D27" s="21" t="str">
+      <c r="D27" s="21">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E27" s="21" t="str">
+        <v>180</v>
+      </c>
+      <c r="E27" s="21">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F27" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G27" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H27" s="21" t="str">
+        <v>46.036245708942204</v>
+      </c>
+      <c r="F27" s="21">
+        <f t="shared" si="5"/>
+        <v>133.9637542910578</v>
+      </c>
+      <c r="G27" s="21">
+        <f t="shared" si="4"/>
+        <v>14648.809541294238</v>
+      </c>
+      <c r="H27" s="21">
         <f t="shared" si="2"/>
-        <v/>
+        <v>3351.1904587057616</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A28" s="2"/>
-      <c r="B28" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A28" s="2">
+        <v>46202</v>
+      </c>
+      <c r="B28" s="23">
+        <f t="shared" si="3"/>
+        <v>27</v>
       </c>
       <c r="C28" s="3"/>
-      <c r="D28" s="4" t="str">
+      <c r="D28" s="4">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E28" s="4" t="str">
+        <v>180</v>
+      </c>
+      <c r="E28" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F28" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G28" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H28" s="4" t="str">
+        <v>45.619058203910434</v>
+      </c>
+      <c r="F28" s="4">
+        <f t="shared" si="5"/>
+        <v>134.38094179608956</v>
+      </c>
+      <c r="G28" s="4">
+        <f t="shared" si="4"/>
+        <v>14514.428599498149</v>
+      </c>
+      <c r="H28" s="4">
         <f t="shared" si="2"/>
-        <v/>
+        <v>3485.5714005018508</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A29" s="19"/>
-      <c r="B29" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A29" s="19">
+        <v>46202</v>
+      </c>
+      <c r="B29" s="24">
+        <f t="shared" si="3"/>
+        <v>28</v>
       </c>
       <c r="C29" s="20"/>
-      <c r="D29" s="21" t="str">
+      <c r="D29" s="21">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E29" s="21" t="str">
+        <v>180</v>
+      </c>
+      <c r="E29" s="21">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F29" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G29" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H29" s="21" t="str">
+        <v>45.200571501082401</v>
+      </c>
+      <c r="F29" s="21">
+        <f t="shared" si="5"/>
+        <v>134.79942849891759</v>
+      </c>
+      <c r="G29" s="21">
+        <f t="shared" si="4"/>
+        <v>14379.629170999231</v>
+      </c>
+      <c r="H29" s="21">
         <f t="shared" si="2"/>
-        <v/>
+        <v>3620.3708290007689</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A30" s="2"/>
-      <c r="B30" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A30" s="2">
+        <v>46202</v>
+      </c>
+      <c r="B30" s="23">
+        <f t="shared" si="3"/>
+        <v>29</v>
       </c>
       <c r="C30" s="3"/>
-      <c r="D30" s="4" t="str">
+      <c r="D30" s="4">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E30" s="4" t="str">
+        <v>180</v>
+      </c>
+      <c r="E30" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F30" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G30" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H30" s="4" t="str">
+        <v>44.78078155451977</v>
+      </c>
+      <c r="F30" s="4">
+        <f t="shared" si="5"/>
+        <v>135.21921844548024</v>
+      </c>
+      <c r="G30" s="4">
+        <f t="shared" si="4"/>
+        <v>14244.409952553751</v>
+      </c>
+      <c r="H30" s="4">
         <f t="shared" si="2"/>
-        <v/>
+        <v>3755.5900474462487</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A31" s="19"/>
-      <c r="B31" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A31" s="19">
+        <v>46202</v>
+      </c>
+      <c r="B31" s="24">
+        <f t="shared" si="3"/>
+        <v>30</v>
       </c>
       <c r="C31" s="20"/>
-      <c r="D31" s="21" t="str">
+      <c r="D31" s="21">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E31" s="21" t="str">
+        <v>180</v>
+      </c>
+      <c r="E31" s="21">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F31" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G31" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H31" s="21" t="str">
+        <v>44.359684305684446</v>
+      </c>
+      <c r="F31" s="21">
+        <f t="shared" si="5"/>
+        <v>135.64031569431555</v>
+      </c>
+      <c r="G31" s="21">
+        <f t="shared" si="4"/>
+        <v>14108.769636859435</v>
+      </c>
+      <c r="H31" s="21">
         <f t="shared" si="2"/>
-        <v/>
+        <v>3891.2303631405648</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A32" s="2"/>
-      <c r="B32" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A32" s="2">
+        <v>46202</v>
+      </c>
+      <c r="B32" s="23">
+        <f t="shared" si="3"/>
+        <v>31</v>
       </c>
       <c r="C32" s="3"/>
-      <c r="D32" s="4" t="str">
+      <c r="D32" s="4">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E32" s="4" t="str">
+        <v>180</v>
+      </c>
+      <c r="E32" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F32" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G32" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H32" s="4" t="str">
+        <v>43.937275683399292</v>
+      </c>
+      <c r="F32" s="4">
+        <f t="shared" si="5"/>
+        <v>136.06272431660071</v>
+      </c>
+      <c r="G32" s="4">
+        <f t="shared" si="4"/>
+        <v>13972.706912542835</v>
+      </c>
+      <c r="H32" s="4">
         <f t="shared" si="2"/>
-        <v/>
+        <v>4027.2930874571648</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" s="19"/>
-      <c r="B33" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A33" s="19">
+        <v>46203</v>
+      </c>
+      <c r="B33" s="24">
+        <f t="shared" si="3"/>
+        <v>32</v>
       </c>
       <c r="C33" s="20"/>
-      <c r="D33" s="21" t="str">
+      <c r="D33" s="21">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E33" s="21" t="str">
+        <v>180</v>
+      </c>
+      <c r="E33" s="21">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F33" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G33" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H33" s="21" t="str">
+        <v>43.513551603808779</v>
+      </c>
+      <c r="F33" s="21">
+        <f t="shared" si="5"/>
+        <v>136.48644839619124</v>
+      </c>
+      <c r="G33" s="21">
+        <f t="shared" si="4"/>
+        <v>13836.220464146643</v>
+      </c>
+      <c r="H33" s="21">
         <f t="shared" si="2"/>
-        <v/>
+        <v>4163.7795358533567</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" s="2"/>
-      <c r="B34" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A34" s="2">
+        <v>46204</v>
+      </c>
+      <c r="B34" s="23">
+        <f t="shared" si="3"/>
+        <v>33</v>
       </c>
       <c r="C34" s="3"/>
-      <c r="D34" s="4" t="str">
+      <c r="D34" s="4">
         <f t="shared" ref="D34:D65" si="6">IF(AND($A34&lt;&gt;"",$B34&lt;&gt;""),$K$9,"")</f>
-        <v/>
-      </c>
-      <c r="E34" s="4" t="str">
+        <v>180</v>
+      </c>
+      <c r="E34" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F34" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G34" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H34" s="4" t="str">
+        <v>43.088507970339514</v>
+      </c>
+      <c r="F34" s="4">
+        <f t="shared" si="5"/>
+        <v>136.91149202966048</v>
+      </c>
+      <c r="G34" s="4">
+        <f t="shared" si="4"/>
+        <v>13699.308972116984</v>
+      </c>
+      <c r="H34" s="4">
         <f t="shared" si="2"/>
-        <v/>
+        <v>4300.6910278830164</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Renita_Daily.xlsx
+++ b/NBFC-MF/Borrowers/Renita_Daily.xlsx
@@ -1146,7 +1146,7 @@
       </c>
       <c r="K12" s="10">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="K13" s="12">
         <f>(K10*K9)-K9*K12</f>
-        <v>15660</v>
+        <v>15480</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="K14" s="12">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>13699.308972116984</v>
+        <v>13561.971112790645</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="K15" s="14">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>4300.6910278830164</v>
+        <v>4438.0288872093552</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
@@ -1847,31 +1847,33 @@
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" s="19"/>
-      <c r="B35" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A35" s="19">
+        <v>46205</v>
+      </c>
+      <c r="B35" s="24">
+        <f t="shared" si="3"/>
+        <v>34</v>
       </c>
       <c r="C35" s="20"/>
-      <c r="D35" s="21" t="str">
+      <c r="D35" s="21">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E35" s="21" t="str">
+        <v>180</v>
+      </c>
+      <c r="E35" s="21">
         <f t="shared" ref="E35:E66" si="7">IF(AND($A35&lt;&gt;"",$B35&lt;&gt;""),G34*$K$8,"")</f>
-        <v/>
-      </c>
-      <c r="F35" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G35" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H35" s="21" t="str">
+        <v>42.662140673660645</v>
+      </c>
+      <c r="F35" s="21">
+        <f t="shared" si="5"/>
+        <v>137.33785932633936</v>
+      </c>
+      <c r="G35" s="21">
+        <f t="shared" si="4"/>
+        <v>13561.971112790645</v>
+      </c>
+      <c r="H35" s="21">
         <f t="shared" ref="H35:H66" si="8">IF(AND($A35&lt;&gt;"",$B35&lt;&gt;""),$K$7-G35,"")</f>
-        <v/>
+        <v>4438.0288872093552</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
